--- a/input.xlsx
+++ b/input.xlsx
@@ -419,28 +419,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>検索キーワード</t>
+          <t>キーワード</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>スターバックス 新宿</t>
+          <t>さいたま市 皮膚科 クリニック</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ユニクロ 渋谷</t>
+          <t>川越市 皮膚科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>マクドナルド 銀座</t>
+          <t>越谷市 皮膚科 クリニック</t>
         </is>
       </c>
     </row>
